--- a/artfynd/A 23807-2026 artfynd.xlsx
+++ b/artfynd/A 23807-2026 artfynd.xlsx
@@ -896,7 +896,7 @@
         <v>133582970</v>
       </c>
       <c r="B4" t="n">
-        <v>97243</v>
+        <v>97245</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 23807-2026 artfynd.xlsx
+++ b/artfynd/A 23807-2026 artfynd.xlsx
@@ -896,7 +896,7 @@
         <v>133582970</v>
       </c>
       <c r="B4" t="n">
-        <v>97245</v>
+        <v>97253</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 23807-2026 artfynd.xlsx
+++ b/artfynd/A 23807-2026 artfynd.xlsx
@@ -896,7 +896,7 @@
         <v>133582970</v>
       </c>
       <c r="B4" t="n">
-        <v>97253</v>
+        <v>97281</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 23807-2026 artfynd.xlsx
+++ b/artfynd/A 23807-2026 artfynd.xlsx
@@ -896,7 +896,7 @@
         <v>133582970</v>
       </c>
       <c r="B4" t="n">
-        <v>97281</v>
+        <v>97291</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 23807-2026 artfynd.xlsx
+++ b/artfynd/A 23807-2026 artfynd.xlsx
@@ -896,7 +896,7 @@
         <v>133582970</v>
       </c>
       <c r="B4" t="n">
-        <v>97291</v>
+        <v>97293</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 23807-2026 artfynd.xlsx
+++ b/artfynd/A 23807-2026 artfynd.xlsx
@@ -896,7 +896,7 @@
         <v>133582970</v>
       </c>
       <c r="B4" t="n">
-        <v>97294</v>
+        <v>97301</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 23807-2026 artfynd.xlsx
+++ b/artfynd/A 23807-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>98310780</v>
       </c>
       <c r="B2" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -700,12 +695,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>751428.067306308</v>
+        <v>751428</v>
       </c>
       <c r="R2" t="n">
-        <v>7295895.615062658</v>
+        <v>7295895</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2021-10-27</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-10-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,48 +772,49 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130828598</v>
+        <v>133582968</v>
       </c>
       <c r="B3" t="n">
-        <v>92180</v>
+        <v>92245</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2062</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Vistån-Vistträsket, Nb</t>
+          <t>Vistbäcken, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>751425</v>
+        <v>751414</v>
       </c>
       <c r="R3" t="n">
-        <v>7295898</v>
+        <v>7295929</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,12 +841,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-06-11</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-06-11</t>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,73 +860,66 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>Gudrun Norstedt</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jonas Nordenström</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133582970</v>
+        <v>130828598</v>
       </c>
       <c r="B4" t="n">
-        <v>97301</v>
+        <v>92281</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2869</v>
+        <v>2062</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Vistbäcken, Nb</t>
+          <t>Vistån-Vistträsket, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>751486</v>
+        <v>751425</v>
       </c>
       <c r="R4" t="n">
-        <v>7295846</v>
+        <v>7295898</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -962,17 +946,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2021-06-11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2021-06-11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,21 +960,239 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>Gudrun Norstedt</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Tyr Nilsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>133582970</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97308</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2869</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Bollvitmossa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Sphagnum wulfianum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Vistbäcken, Nb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>751486</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7295846</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Mimmi Persson</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Mimmi Persson</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>133582969</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80493</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Vistbäcken, Nb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>751523</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7295904</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23807-2026 artfynd.xlsx
+++ b/artfynd/A 23807-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98310780</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582968</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -981,6 +996,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130828598</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1087,6 +1107,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582970</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1193,8 +1218,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582969</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>